--- a/site/exports/whu-eis.xlsx
+++ b/site/exports/whu-eis.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rcb1d816d037a43f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rdd51484ec6f54379"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R941466cb277e4920"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R5ddfab12f79d4054"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Ra016b3bfc7df408f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R663cdfe5bc9a4501"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R988a17a003964cab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R627b5485cb18459c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R8a4ca047cf914db6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Rbb3ac60b417248d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,17 +139,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T46_0" displayName="T46_0" ref="A1:K3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T52_0" displayName="T52_0" ref="A1:K6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
     <x:tableColumn id="3" name="院系"/>
-    <x:tableColumn id="4" name="官方主页"/>
+    <x:tableColumn id="4" name="个人主页／职业网站（来源类型见说明）"/>
     <x:tableColumn id="5" name="核对日期"/>
     <x:tableColumn id="6" name="缺项与冲突"/>
     <x:tableColumn id="7" name="范围"/>
     <x:tableColumn id="8" name="主页可用性"/>
-    <x:tableColumn id="9" name="替代官方职业报道（非个人主页）"/>
+    <x:tableColumn id="9" name="替代职业资料来源（非已核个人主页）"/>
     <x:tableColumn id="10" name="所属学校ID"/>
     <x:tableColumn id="11" name="所属学校"/>
   </x:tableColumns>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T46_1" displayName="T46_1" ref="A1:S15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T52_1" displayName="T52_1" ref="A1:S21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T46_3" displayName="T46_3" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T52_3" displayName="T52_3" ref="A1:L6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T46_4" displayName="T46_4" ref="A1:G8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T52_4" displayName="T52_4" ref="A1:G19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -417,12 +417,12 @@
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="26" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="55" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="55" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="55" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="26" hidden="0" customWidth="1"/>
   </x:cols>
@@ -438,7 +438,7 @@
         <x:v>院系</x:v>
       </x:c>
       <x:c r="D1" s="9" t="str">
-        <x:v>官方主页</x:v>
+        <x:v>个人主页／职业网站（来源类型见说明）</x:v>
       </x:c>
       <x:c r="E1" s="9" t="str">
         <x:v>核对日期</x:v>
@@ -453,7 +453,7 @@
         <x:v>主页可用性</x:v>
       </x:c>
       <x:c r="I1" s="9" t="str">
-        <x:v>替代官方职业报道（非个人主页）</x:v>
+        <x:v>替代职业资料来源（非已核个人主页）</x:v>
       </x:c>
       <x:c r="J1" s="9" t="str">
         <x:v>所属学校ID</x:v>
@@ -528,10 +528,103 @@
         <x:v>武汉大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="4" ht="64" customHeight="1">
+      <x:c r="A4" s="6" t="str">
+        <x:v>陈淑珍</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="str">
+        <x:v>电子信息学院</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str"/>
+      <x:c r="E4" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>学历院校、专业、起止日期及明确授位状态未由已实读本人页披露；学历标签不作为985学位筛选依据。；本人各阶段导师无直接证据，mentors为空，不由共同作者或学生反推。；具体校区未核，不从通信地址推定。；仅部分职业事实及精选书目，不是完整履历或论文全集。；陈淑珍本人论文栏目web cache miss、普通读取超时；只使用已成功实读出版社单篇书目。</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="str">
+        <x:v>个人页当前不可达或正文未核；保留既有分级职业证据，不重试受限来源</x:v>
+      </x:c>
+      <x:c r="I4" s="6" t="str"/>
+      <x:c r="J4" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="64" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>代永红</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
+        <x:v>电子信息学院</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str"/>
+      <x:c r="E5" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>学历院校、专业、起止日期及明确授位状态未由已实读本人页披露；学历标签不作为985学位筛选依据。；本人各阶段导师无直接证据，mentors为空，不由共同作者或学生反推。；具体校区未核，不从通信地址推定。；仅部分职业事实及精选书目，不是完整履历或论文全集。；未由出版社检索摘要补入未实读正文的学历院校；可待后续正文可读时核验。</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H5" s="6" t="str">
+        <x:v>个人页当前不可达或正文未核；保留既有分级职业证据，不重试受限来源</x:v>
+      </x:c>
+      <x:c r="I5" s="6" t="str"/>
+      <x:c r="J5" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="K5" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="64" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>何平安</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str">
+        <x:v>电子信息学院</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str"/>
+      <x:c r="E6" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>学历院校、专业、起止日期及明确授位状态未由已实读本人页披露；学历标签不作为985学位筛选依据。；本人各阶段导师无直接证据，mentors为空，不由共同作者或学生反推。；具体校区未核，不从通信地址推定。；仅部分职业事实及精选书目，不是完整履历或论文全集。；本人个人简介、教育经历和工作经历栏目暂无内容；“研究生毕业”不足以区分硕士或博士。精选论文只由同院官方合作者书目证实。</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>个人页当前不可达或正文未核；保留既有分级职业证据，不重试受限来源</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str"/>
+      <x:c r="J6" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="K6" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae82808f65674a85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb20109eefbd496b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1232,10 +1325,234 @@
         <x:v>武汉大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="16" ht="64" customHeight="1">
+      <x:c r="A16" s="6" t="str">
+        <x:v>陈淑珍</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>education_background</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str"/>
+      <x:c r="D16" s="6" t="str"/>
+      <x:c r="E16" s="6" t="str"/>
+      <x:c r="F16" s="6" t="str"/>
+      <x:c r="G16" s="6" t="str"/>
+      <x:c r="H16" s="6" t="str"/>
+      <x:c r="I16" s="6" t="str"/>
+      <x:c r="J16" s="6" t="str"/>
+      <x:c r="K16" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L16" s="6" t="str"/>
+      <x:c r="M16" s="7" t="str"/>
+      <x:c r="N16" s="6" t="str"/>
+      <x:c r="O16" s="6" t="str">
+        <x:v>仅保存页面学历标签；无明确授位陈述，不推定学位、授位院校、日期或导师。</x:v>
+      </x:c>
+      <x:c r="P16" s="6" t="str">
+        <x:v>毕业/就读院校未披露，不能从任职学校推定学历院校及地理。</x:v>
+      </x:c>
+      <x:c r="Q16" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/chenshuzhen/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R16" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="S16" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="64" customHeight="1">
+      <x:c r="A17" s="6" t="str">
+        <x:v>陈淑珍</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D17" s="6" t="str">
+        <x:v>武汉大学电子信息学院</x:v>
+      </x:c>
+      <x:c r="E17" s="6" t="str"/>
+      <x:c r="F17" s="6" t="str"/>
+      <x:c r="G17" s="6" t="str"/>
+      <x:c r="H17" s="6" t="str"/>
+      <x:c r="I17" s="6" t="str"/>
+      <x:c r="J17" s="6" t="str"/>
+      <x:c r="K17" s="6" t="str"/>
+      <x:c r="L17" s="6" t="str"/>
+      <x:c r="M17" s="7" t="str"/>
+      <x:c r="N17" s="6" t="str"/>
+      <x:c r="O17" s="6" t="str">
+        <x:v>职称取个人主页；未将页面入职日当作该职称晋升日期。官网明确离退休，结束日期未知，不列当前在岗。</x:v>
+      </x:c>
+      <x:c r="P17" s="6" t="str"/>
+      <x:c r="Q17" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/chenshuzhen/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R17" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="S17" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="64" customHeight="1">
+      <x:c r="A18" s="6" t="str">
+        <x:v>代永红</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D18" s="6" t="str"/>
+      <x:c r="E18" s="6" t="str"/>
+      <x:c r="F18" s="6" t="str"/>
+      <x:c r="G18" s="6" t="str"/>
+      <x:c r="H18" s="6" t="str"/>
+      <x:c r="I18" s="6" t="str"/>
+      <x:c r="J18" s="6" t="str"/>
+      <x:c r="K18" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L18" s="6" t="str"/>
+      <x:c r="M18" s="7" t="str"/>
+      <x:c r="N18" s="6" t="str"/>
+      <x:c r="O18" s="6" t="str">
+        <x:v>仅保存页面学历标签；无明确授位陈述，不推定学位、授位院校、日期或导师。</x:v>
+      </x:c>
+      <x:c r="P18" s="6" t="str">
+        <x:v>毕业/就读院校未披露，不能从任职学校推定学历院校及地理。</x:v>
+      </x:c>
+      <x:c r="Q18" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/daiyonghong/zh_CN/jsxx/491499/jsxx/jsxx.htm</x:v>
+      </x:c>
+      <x:c r="R18" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="S18" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="64" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>代永红</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str">
+        <x:v>武汉大学电子信息学院</x:v>
+      </x:c>
+      <x:c r="E19" s="6" t="str"/>
+      <x:c r="F19" s="6" t="str"/>
+      <x:c r="G19" s="6" t="str"/>
+      <x:c r="H19" s="6" t="str"/>
+      <x:c r="I19" s="6" t="str"/>
+      <x:c r="J19" s="6" t="str"/>
+      <x:c r="K19" s="6" t="str"/>
+      <x:c r="L19" s="6" t="str"/>
+      <x:c r="M19" s="7" t="str"/>
+      <x:c r="N19" s="6" t="str"/>
+      <x:c r="O19" s="6" t="str">
+        <x:v>职称取个人主页；未将页面入职日当作该职称晋升日期。官网明确在职，不推定全职。</x:v>
+      </x:c>
+      <x:c r="P19" s="6" t="str"/>
+      <x:c r="Q19" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/daiyonghong/zh_CN/jsxx/491499/jsxx/jsxx.htm</x:v>
+      </x:c>
+      <x:c r="R19" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="S19" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="64" customHeight="1">
+      <x:c r="A20" s="6" t="str">
+        <x:v>何平安</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>education_background</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str"/>
+      <x:c r="D20" s="6" t="str"/>
+      <x:c r="E20" s="6" t="str"/>
+      <x:c r="F20" s="6" t="str"/>
+      <x:c r="G20" s="6" t="str"/>
+      <x:c r="H20" s="6" t="str"/>
+      <x:c r="I20" s="6" t="str"/>
+      <x:c r="J20" s="6" t="str"/>
+      <x:c r="K20" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L20" s="6" t="str"/>
+      <x:c r="M20" s="7" t="str"/>
+      <x:c r="N20" s="6" t="str"/>
+      <x:c r="O20" s="6" t="str">
+        <x:v>仅保存页面学历标签；无明确授位陈述，不推定学位、授位院校、日期或导师。</x:v>
+      </x:c>
+      <x:c r="P20" s="6" t="str">
+        <x:v>毕业/就读院校未披露，不能从任职学校推定学历院校及地理。</x:v>
+      </x:c>
+      <x:c r="Q20" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/hepingan/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R20" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="S20" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="64" customHeight="1">
+      <x:c r="A21" s="6" t="str">
+        <x:v>何平安</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D21" s="6" t="str">
+        <x:v>武汉大学电子信息学院</x:v>
+      </x:c>
+      <x:c r="E21" s="6" t="str"/>
+      <x:c r="F21" s="6" t="str"/>
+      <x:c r="G21" s="6" t="str"/>
+      <x:c r="H21" s="6" t="str"/>
+      <x:c r="I21" s="6" t="str"/>
+      <x:c r="J21" s="6" t="str"/>
+      <x:c r="K21" s="6" t="str"/>
+      <x:c r="L21" s="6" t="str"/>
+      <x:c r="M21" s="7" t="str"/>
+      <x:c r="N21" s="6" t="str"/>
+      <x:c r="O21" s="6" t="str">
+        <x:v>职称取个人主页；未将页面入职日当作该职称晋升日期。官网明确离退休，结束日期未知，不列当前在岗。</x:v>
+      </x:c>
+      <x:c r="P21" s="6" t="str"/>
+      <x:c r="Q21" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/hepingan/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R21" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="S21" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8beefa899e814552"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5a0ae2530a046a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1429,10 +1746,118 @@
         <x:v>武汉大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="4" ht="64" customHeight="1">
+      <x:c r="A4" s="6" t="str">
+        <x:v>陈淑珍</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>应用Mean Shift和分块的抗遮挡跟踪</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str"/>
+      <x:c r="E4" s="6" t="str">
+        <x:v>https://ope.lightpublishing.cn/zh/article/1752930/</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>期刊论文；journal_article</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>https://ope.lightpublishing.cn/zh/article/1752930/</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="str">
+        <x:v>出版方中文姓名与武汉大学电子信息学院明确对应；官网本人页姓名及单位一致。</x:v>
+      </x:c>
+      <x:c r="I4" s="6" t="str">
+        <x:v>出版社文章元数据已核，不表示全文已读。；article_metadata_verified</x:v>
+      </x:c>
+      <x:c r="J4" s="6" t="str">
+        <x:v>出版方页面明确作者陈淑珍及唯一作者机构武汉大学电子信息学院，18(6):1413–1419；DOI栏为空。论文栏目读取失败，不代表本人无论文。</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="L4" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="64" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>代永红</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>高速空间相干光平衡探测器结构优化</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str"/>
+      <x:c r="E5" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/daiyonghong/zh_CN/lwcg/491502/content/45299.htm</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>期刊论文；journal_article</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/daiyonghong/zh_CN/lwcg/491502/content/45299.htm</x:v>
+      </x:c>
+      <x:c r="H5" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/daiyonghong/zh_CN/lwcg/491502/list/index.htm</x:v>
+      </x:c>
+      <x:c r="I5" s="6" t="str">
+        <x:v>先前成功读取的官方单篇元数据；本轮未能二次打开，未核出版社或全文。；official_individual_publication_metadata_verified</x:v>
+      </x:c>
+      <x:c r="J5" s="6" t="str">
+        <x:v>本人论文栏目直接链接的单篇元数据已读，25(10)；采用书目年2017，不把主页元数据2017-01-01当精确出版日；DOI未披露。</x:v>
+      </x:c>
+      <x:c r="K5" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="L5" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="64" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>何平安</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>基于超表面材料的光波相位精密操控新技术</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str"/>
+      <x:c r="E6" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/zhengguoxing/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>期刊论文；journal_article</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/zhengguoxing/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>同院合作者官方主页论文列表明确中文姓名何平安，结合本人主页同院任职匹配；未以第三方聚合学者库拼接。</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str">
+        <x:v>仅官方合著者书目所列条目，未核出版社落地页或全文。；official_coauthor_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J6" s="6" t="str">
+        <x:v>同院合作者郑国兴官方主页明确列何平安为共同作者，38(2):153–158；该书目链接的出版社页robots.txt不可达，未核单篇元数据或DOI，不把共同作者当导师。</x:v>
+      </x:c>
+      <x:c r="K6" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="L6" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R459465a67fc542b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd745875b8887475e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1590,16 +2015,16 @@
     </x:row>
     <x:row r="7" ht="64" customHeight="1">
       <x:c r="A7" s="6" t="str">
-        <x:v>曹小毛</x:v>
+        <x:v>陈淑珍</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
-        <x:v>institution-classification-2</x:v>
+        <x:v>chenshuzhen-source-1</x:v>
       </x:c>
       <x:c r="C7" s="6" t="str">
-        <x:v>https://www.whu.edu.cn/xxgk/xxjj.htm</x:v>
+        <x:v>https://jszy.whu.edu.cn/xyjslb.jsp?PAGENUM=1&amp;id=2013&amp;lang=zh_CN&amp;st=0&amp;totalpage=4&amp;urltype=tsites.CollegeTeacherList&amp;wbtreeid=1006</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>官方名录内容已读，仅保存本批选中观察。；official_roster_read</x:v>
       </x:c>
       <x:c r="E7" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -1613,16 +2038,16 @@
     </x:row>
     <x:row r="8" ht="64" customHeight="1">
       <x:c r="A8" s="6" t="str">
-        <x:v>陈景东</x:v>
+        <x:v>陈淑珍</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>institution-classification-3</x:v>
+        <x:v>chenshuzhen-source-2</x:v>
       </x:c>
       <x:c r="C8" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://jszy.whu.edu.cn/chenshuzhen/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>先前成功实读的官方职业字段或元数据已读回；本轮页面不可达，未二次读取正文。；official_university_hosted_profile_body_read</x:v>
       </x:c>
       <x:c r="E8" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -1631,13 +2056,266 @@
         <x:v>whu</x:v>
       </x:c>
       <x:c r="G8" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="64" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>陈淑珍</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>chenshuzhen-source-3</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str">
+        <x:v>https://ope.lightpublishing.cn/zh/article/1752930/</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>出版者单篇文章元数据正文已读，不表示全文已核。；official_publisher_article_metadata_body_read</x:v>
+      </x:c>
+      <x:c r="E9" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="G9" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="64" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>代永红</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>daiyonghong-source-1</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/xyjslb.jsp?PAGENUM=1&amp;id=2013&amp;lang=zh_CN&amp;st=0&amp;totalpage=4&amp;urltype=tsites.CollegeTeacherList&amp;wbtreeid=1006</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>官方名录内容已读，仅保存本批选中观察。；official_roster_read</x:v>
+      </x:c>
+      <x:c r="E10" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F10" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="G10" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="64" customHeight="1">
+      <x:c r="A11" s="6" t="str">
+        <x:v>代永红</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>daiyonghong-source-2</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/daiyonghong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>先前成功实读的官方职业字段或元数据已读回；本轮页面不可达，未二次读取正文。；official_university_hosted_profile_body_read</x:v>
+      </x:c>
+      <x:c r="E11" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="G11" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="64" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>代永红</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>daiyonghong-source-3</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/daiyonghong/zh_CN/jsxx/491499/jsxx/jsxx.htm</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>先前成功实读的官方职业字段或元数据已读回；本轮页面不可达，未二次读取正文。；official_university_hosted_profile_body_read</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F12" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="G12" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="64" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>代永红</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>daiyonghong-source-4</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/daiyonghong/zh_CN/lwcg/491502/list/index.htm</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>先前成功实读的官方职业字段或元数据已读回；本轮页面不可达，未二次读取正文。；official_university_hosted_publication_list_body_read</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F13" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="G13" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="64" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>代永红</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>daiyonghong-source-5</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/daiyonghong/zh_CN/lwcg/491502/content/45299.htm</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>先前成功实读的官方职业字段或元数据已读回；本轮页面不可达，未二次读取正文。；official_university_hosted_individual_publication_metadata_body_read</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F14" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="G14" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="64" customHeight="1">
+      <x:c r="A15" s="6" t="str">
+        <x:v>何平安</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="str">
+        <x:v>hepingan-source-1</x:v>
+      </x:c>
+      <x:c r="C15" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/xyjslb.jsp?PAGENUM=1&amp;id=2013&amp;lang=zh_CN&amp;st=0&amp;totalpage=4&amp;urltype=tsites.CollegeTeacherList&amp;wbtreeid=1006</x:v>
+      </x:c>
+      <x:c r="D15" s="6" t="str">
+        <x:v>官方名录内容已读，仅保存本批选中观察。；official_roster_read</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F15" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="G15" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="64" customHeight="1">
+      <x:c r="A16" s="6" t="str">
+        <x:v>何平安</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>hepingan-source-2</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/hepingan/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="str">
+        <x:v>先前成功实读的官方职业字段或元数据已读回；本轮页面不可达，未二次读取正文。；official_university_hosted_profile_body_read</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F16" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="G16" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="64" customHeight="1">
+      <x:c r="A17" s="6" t="str">
+        <x:v>何平安</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>hepingan-source-3</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="str">
+        <x:v>https://jszy.whu.edu.cn/zhengguoxing/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="D17" s="6" t="str">
+        <x:v>同院官方合作者主页书目已读，非本人页或出版者单篇核验。；official_coauthor_profile_publication_list_body_read</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F17" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="G17" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="64" customHeight="1">
+      <x:c r="A18" s="6" t="str">
+        <x:v>曹小毛</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="str">
+        <x:v>https://www.whu.edu.cn/xxgk/xxjj.htm</x:v>
+      </x:c>
+      <x:c r="D18" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F18" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="G18" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="64" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>陈景东</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F19" s="6" t="str">
+        <x:v>whu</x:v>
+      </x:c>
+      <x:c r="G19" s="6" t="str">
         <x:v>武汉大学</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re285e4df967a4a74"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb788e2248164176"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/whu-eis.xlsx
+++ b/site/exports/whu-eis.xlsx
@@ -452,7 +452,7 @@
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18.2" customWidth="1" min="7" max="7"/>
+    <col width="37.8" customWidth="1" min="7" max="7"/>
     <col width="44.8" customWidth="1" min="8" max="8"/>
     <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -651,7 +651,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
